--- a/artfynd/A 48772-2024 artfynd.xlsx
+++ b/artfynd/A 48772-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>104846681</v>
       </c>
       <c r="B2" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>526383.7934124166</v>
+        <v>526384</v>
       </c>
       <c r="R2" t="n">
-        <v>6986499.865787155</v>
+        <v>6986500</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104846680</v>
+        <v>104846682</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>526388.7420477236</v>
+        <v>526333</v>
       </c>
       <c r="R3" t="n">
-        <v>6986506.720314162</v>
+        <v>6986447</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,7 +855,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -901,6 +870,108 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104846680</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SV Knackåstjärn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>526389</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6986507</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 48772-2024 artfynd.xlsx
+++ b/artfynd/A 48772-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846681</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846682</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,8 +991,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104846680</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>